--- a/docs/assets/3rdparty/source/icecream-flavours-IDs.xlsx
+++ b/docs/assets/3rdparty/source/icecream-flavours-IDs.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leskneebone/Projects/docs/docs/assets/3rdparty/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B5A3177-FB3A-4048-8919-140D362CD47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F10B3344-23E4-B14A-B37F-05775AC54BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="1620" windowWidth="27640" windowHeight="16600" xr2:uid="{D8F5B238-1CA9-2345-B0A6-1E95D04ABAF3}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="17100" xr2:uid="{D8F5B238-1CA9-2345-B0A6-1E95D04ABAF3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -86,15 +86,9 @@
     <t>Bubblegum</t>
   </si>
   <si>
-    <t>Butter Brickle was the registered trademark of a toffee ice cream flavoring and of a toffee-centered chocolate-covered candy bar similar to the Heath bar, introduced by the Blackstone Hotel in Omaha, Nebraska, in the 1920s. Alternately, it is often prepared and sold as butter vanilla-flavored ice cream with tiny flecks of butter toffee instead of chunks of Heath bar.</t>
-  </si>
-  <si>
     <t>Butterscotch</t>
   </si>
   <si>
-    <t>Butter pecan is a smooth vanilla ice cream with a slight buttery flavor, with pecans added.</t>
-  </si>
-  <si>
     <t>Cake batter</t>
   </si>
   <si>
@@ -182,63 +176,6 @@
     <t>Taro</t>
   </si>
   <si>
-    <t>Cherry - includes variations (e.g. Amaretto cherry, black cherry)</t>
-  </si>
-  <si>
-    <t>Lúcuma - a popular Peruvian ice cream flavor with an orange color and a sweet nutty taste</t>
-  </si>
-  <si>
-    <t>Moon mist - a blend of grape, banana, and blue raspberry (or sometimes bubblegum) flavors, popular in Atlantic Canada. The flavors are generally blended together to give a mist-like texture.</t>
-  </si>
-  <si>
-    <t>Raspberry ripple - consists of raspberry syrup injected into vanilla ice cream.</t>
-  </si>
-  <si>
-    <t>Tiger tail - a flavor popular in Canada, consisting of orange-flavored ice cream with swirls of black licorice</t>
-  </si>
-  <si>
-    <t>Biscuit Tortoni - an ice cream made with eggs and heavy cream, often containing chopped cherries or topped with minced almonds or crumbled macaroons</t>
-  </si>
-  <si>
-    <t>Blue moon - an ice cream flavor with bright blue coloring, available in the Upper Midwest of the United States</t>
-  </si>
-  <si>
-    <t>Chocolate chip - vanilla base, with chunks of solid chocolate. Declining in popularity in the 2020s. Sometimes chocolate ice cream was used, which was usually called "Chocolate chocolate chip"</t>
-  </si>
-  <si>
-    <t>Goody Goody Gum Drops - unique to New Zealand</t>
-  </si>
-  <si>
-    <t>Hokey pokey - a flavor of ice cream in New Zealand, consisting of plain vanilla ice cream with small, solid lumps of honeycomb toffee</t>
-  </si>
-  <si>
-    <t>Mint chocolate chip - composed of mint ice cream with small chocolate chips. In some cases the liqueur crème de menthe is used to provide the mint flavor, but in most cases peppermint or spearmint flavoring is used.</t>
-  </si>
-  <si>
-    <t>Neapolitan - composed of vanilla, chocolate and strawberry ice cream together side by side</t>
-  </si>
-  <si>
-    <t>Rocky road - although there are variations from the original flavor, it is traditionally composed of chocolate ice cream, nuts, and whole or diced marshmallows, or sometimes replaced with marshmallow creme, a more fluid version</t>
-  </si>
-  <si>
-    <t>Spumoni - a molded Italian ice cream made with layers of different colors and flavors, usually containing candied fruits and nuts.</t>
-  </si>
-  <si>
-    <t>Tramontana - composed of dark chocolate, white chocolate, dulce de leche and cookies.</t>
-  </si>
-  <si>
-    <t>Bacon - a modern invention, generally created by adding bacon to egg custard and freezing the mixture</t>
-  </si>
-  <si>
-    <t>Crab - a Japanese creation,it is described as having a sweet taste; the island of Hokkaido, Japan, is known for manufacturing it</t>
-  </si>
-  <si>
-    <t>Spundekäs - based on the German cream cheese of the same name</t>
-  </si>
-  <si>
-    <t>Ube (purple yam) - a popular ice cream flavor in the Philippines</t>
-  </si>
-  <si>
     <t>CHOCOLATE, NUTS AND OTHER SWEETS</t>
   </si>
   <si>
@@ -249,6 +186,69 @@
   </si>
   <si>
     <t>FLAVOR NAMES</t>
+  </si>
+  <si>
+    <t>Cherry : includes variations (e.g. Amaretto cherry, black cherry)</t>
+  </si>
+  <si>
+    <t>Lúcuma : a popular Peruvian ice cream flavor with an orange color and a sweet nutty taste</t>
+  </si>
+  <si>
+    <t>Raspberry ripple : consists of raspberry syrup injected into vanilla ice cream.</t>
+  </si>
+  <si>
+    <t>Biscuit Tortoni : an ice cream made with eggs and heavy cream, often containing chopped cherries or topped with minced almonds or crumbled macaroons</t>
+  </si>
+  <si>
+    <t>Blue moon : an ice cream flavor with bright blue coloring, available in the Upper Midwest of the United States</t>
+  </si>
+  <si>
+    <t>Butter pecan : a smooth vanilla ice cream with a slight buttery flavor, with pecans added.</t>
+  </si>
+  <si>
+    <t>Butter Brickle : the registered trademark of a toffee ice cream flavoring and of a toffee-centered chocolate-covered candy bar similar to the Heath bar, introduced by the Blackstone Hotel in Omaha, Nebraska, in the 1920s. Alternately, it is often prepared and sold as butter vanilla-flavored ice cream with tiny flecks of butter toffee instead of chunks of Heath bar.</t>
+  </si>
+  <si>
+    <t>Chocolate chip : vanilla base, with chunks of solid chocolate. Declining in popularity in the 2020s. Sometimes chocolate ice cream was used, which was usually called "Chocolate chocolate chip"</t>
+  </si>
+  <si>
+    <t>Goody Goody Gum Drops : unique to New Zealand</t>
+  </si>
+  <si>
+    <t>Hokey pokey : a flavor of ice cream in New Zealand, consisting of plain vanilla ice cream with small, solid lumps of honeycomb toffee</t>
+  </si>
+  <si>
+    <t>Mint chocolate chip : composed of mint ice cream with small chocolate chips. In some cases the liqueur crème de menthe is used to provide the mint flavor, but in most cases peppermint or spearmint flavoring is used.</t>
+  </si>
+  <si>
+    <t>Neapolitan : composed of vanilla, chocolate and strawberry ice cream together side by side</t>
+  </si>
+  <si>
+    <t>Rocky road : although there are variations from the original flavor, it is traditionally composed of chocolate ice cream, nuts, and whole or diced marshmallows, or sometimes replaced with marshmallow creme, a more fluid version</t>
+  </si>
+  <si>
+    <t>Spumoni : a molded Italian ice cream made with layers of different colors and flavors, usually containing candied fruits and nuts.</t>
+  </si>
+  <si>
+    <t>Tramontana : composed of dark chocolate, white chocolate, dulce de leche and cookies.</t>
+  </si>
+  <si>
+    <t>Bacon : a modern invention, generally created by adding bacon to egg custard and freezing the mixture</t>
+  </si>
+  <si>
+    <t>Crab : a Japanese creation,it is described as having a sweet taste; the island of Hokkaido, Japan, is known for manufacturing it</t>
+  </si>
+  <si>
+    <t>Ube (purple yam) : a popular ice cream flavor in the Philippines</t>
+  </si>
+  <si>
+    <t>Tiger tail : a flavor popular in Canada, consisting of orange-flavored ice cream with swirls of black licorice</t>
+  </si>
+  <si>
+    <t>Moon mist : a blend of grape, banana, and blue raspberry (or sometimes bubblegum) flavors, popular in Atlantic Canada. The flavors are generally blended together to give a mist-like texture.</t>
+  </si>
+  <si>
+    <t>Spundekas : based on the German cream cheese of the same name</t>
   </si>
 </sst>
 </file>
@@ -628,368 +628,683 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FF9460-F418-CA44-84AF-DE772B3A7DA8}">
-  <dimension ref="A1:A74"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35.1640625" customWidth="1"/>
+    <col min="1" max="1" width="48.1640625" customWidth="1"/>
+    <col min="2" max="2" width="35.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B1" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="str">
+        <f ca="1">LOWER(_xlfn.CONCAT(
+DEC2HEX(RANDBETWEEN(0,POWER(16,8)-1),8),"-",
+DEC2HEX(RANDBETWEEN(0,POWER(16,4)-1),4),"-",
+"4",DEC2HEX(RANDBETWEEN(0,POWER(16,3)-1),3),"-",
+DEC2HEX(RANDBETWEEN(8,11)),DEC2HEX(RANDBETWEEN(0,POWER(16,3)-1),3),"-",
+DEC2HEX(RANDBETWEEN(0,POWER(16,8)-1),8),
+DEC2HEX(RANDBETWEEN(0,POWER(16,4)-1),4)
+))</f>
+        <v>7b160f84-361e-417f-aef3-57aaae778e36</v>
+      </c>
+      <c r="B3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="str">
+        <f t="shared" ref="A4:A67" ca="1" si="0">LOWER(_xlfn.CONCAT(
+DEC2HEX(RANDBETWEEN(0,POWER(16,8)-1),8),"-",
+DEC2HEX(RANDBETWEEN(0,POWER(16,4)-1),4),"-",
+"4",DEC2HEX(RANDBETWEEN(0,POWER(16,3)-1),3),"-",
+DEC2HEX(RANDBETWEEN(8,11)),DEC2HEX(RANDBETWEEN(0,POWER(16,3)-1),3),"-",
+DEC2HEX(RANDBETWEEN(0,POWER(16,8)-1),8),
+DEC2HEX(RANDBETWEEN(0,POWER(16,4)-1),4)
+))</f>
+        <v>1b7d67e9-7f1a-4a51-b91e-b44e17e31c2c</v>
+      </c>
+      <c r="B4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>f6e273e7-23c8-4cad-92dd-cb9663349b47</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>04e3aad9-422b-48d0-b43d-80d1e28a7f46</v>
+      </c>
+      <c r="B6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>170146c4-0f42-4414-91ba-61a9198efc79</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>cf80d51f-821e-446c-aeab-58b80859ed49</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>5b03de59-40ab-4862-b9ea-927eaa017e60</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>4e8018c9-6ac8-4649-8e6d-dd07f4c8bbb1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>00041781-f8a3-4959-8389-e5ddd1713226</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>19de5e74-293a-4e85-9b55-67d0b8e933e5</v>
+      </c>
+      <c r="B12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>44de53ec-9ce7-4c80-bc3d-7020c37b6133</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>bbea3fe3-1c39-4066-a0ab-99f2ccb53628</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>7bff714f-d9d9-473b-9ff9-19d4941eb65a</v>
+      </c>
+      <c r="B15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>78d3eb98-963b-4af5-8787-6a1619685c48</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>8bd965d2-3c49-46f4-92f0-e65eb65b6d7a</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>062de6fa-38dc-4ebb-b239-1e51d3b89303</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>1b0cc14e-ab5f-4d1a-a3ed-b3fa1df250eb</v>
+      </c>
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>9804cdc4-7623-4714-8002-b95bfa42f4f6</v>
+      </c>
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>d22483e3-e9a4-4e9a-8739-736b57049f01</v>
+      </c>
+      <c r="B21" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>ca11c2ce-1468-4107-8d63-95e3a3ec889f</v>
+      </c>
+      <c r="B22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>e7c665fc-e38e-4fb0-9e5b-4c422ba97512</v>
+      </c>
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>5b98668e-5454-430c-aa5b-0b266f840269</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>f9ec744d-4313-46cf-b847-70cb510d31d7</v>
+      </c>
+      <c r="B25" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>0cb6ff0e-dd72-4899-8364-60bb57935985</v>
+      </c>
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>0c5d8692-2484-437b-b0eb-d2ea4666dfe9</v>
+      </c>
+      <c r="B27" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>ec8bdca2-5804-4814-a051-9a3dea143f2d</v>
+      </c>
+      <c r="B28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>057108ce-4561-4708-bb16-c97b070c9174</v>
+      </c>
+      <c r="B29" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>7dfbb71b-4ce1-42a9-bf92-d783499cf216</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>23f62340-3f68-4d5e-b6a6-9807cadc3ca6</v>
+      </c>
+      <c r="B31" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>fa098773-8ea0-4b7f-9eef-c905a6079a57</v>
+      </c>
+      <c r="B32" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>1807ea36-1fea-440a-b44e-ad73aa35d804</v>
+      </c>
+      <c r="B33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>e450e82a-80de-4892-81ef-47f347c90810</v>
+      </c>
+      <c r="B34" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2d341970-764b-412e-8d1f-74e8a0e4258d</v>
+      </c>
+      <c r="B35" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>a67b7766-0678-4d7f-9f51-c5c7bfb69bdf</v>
+      </c>
+      <c r="B36" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>25444a85-caa1-4f0a-a1a2-c1bdfacd68ea</v>
+      </c>
+      <c r="B37" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>86f37cd2-ade6-4cec-b74e-51a49099be97</v>
+      </c>
+      <c r="B38" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>4e98b000-1c77-42a8-be9d-41f26e98a83b</v>
+      </c>
+      <c r="B39" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>1bb203c3-6c4e-4f09-bbdc-459d96a4a202</v>
+      </c>
+      <c r="B40" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>12bfaf5a-5e2f-40b2-a74f-b92fe565c1e6</v>
+      </c>
+      <c r="B41" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>64ea1a0f-f5b8-45c2-a516-57a5c7c67c31</v>
+      </c>
+      <c r="B42" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>8a47be0e-71c8-4793-9ffb-d0eae6d4918f</v>
+      </c>
+      <c r="B43" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>9ba2647c-2eb0-43d9-a63e-f80c01d5a170</v>
+      </c>
+      <c r="B44" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>888a8366-9523-4cb7-b268-d85ccfc9c390</v>
+      </c>
+      <c r="B45" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>e343fee9-c50e-488c-9040-3c1ad0208292</v>
+      </c>
+      <c r="B46" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>59c5f961-5b89-4a6b-93e4-f884377255b1</v>
+      </c>
+      <c r="B47" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>d890d2f8-83b0-45f8-88a2-c96df44dfc52</v>
+      </c>
+      <c r="B48" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>08212cd3-3985-4c45-adc6-6d8955f210c3</v>
+      </c>
+      <c r="B49" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>a948bd7f-a30e-4bad-b595-3a45b10b0db0</v>
+      </c>
+      <c r="B50" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>ca4bb557-abf8-44d8-a24d-6ac5277c6ff5</v>
+      </c>
+      <c r="B51" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>f58cc31e-5820-4405-8f7e-aefda29dd5ac</v>
+      </c>
+      <c r="B52" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>98960d08-12e5-40b0-90c5-0c37a2a17a9c</v>
+      </c>
+      <c r="B53" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>47ab46a8-1e05-4676-b2ba-447ca72d7ef2</v>
+      </c>
+      <c r="B54" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>a72efc96-e261-446a-ac49-784712bd4011</v>
+      </c>
+      <c r="B55" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>5db09078-d358-4962-96d8-04a176e3e891</v>
+      </c>
+      <c r="B56" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>d130fffe-5b33-48da-bb69-7bcbe3b25aa2</v>
+      </c>
+      <c r="B57" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>c44927ad-c1d8-46ab-97ce-b661fc446158</v>
+      </c>
+      <c r="B58" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>b6efc05c-2ee7-4633-aadb-2b2939e43614</v>
+      </c>
+      <c r="B59" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>f58d780a-ca40-4782-a752-cbc64cc41350</v>
+      </c>
+      <c r="B60" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>b001266b-ef05-4572-827e-c979de02018a</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>beebca3e-8f17-48ed-9f2f-8c981e849127</v>
+      </c>
+      <c r="B62" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>ee4ffef7-7b92-4313-ba03-b75685cfa35f</v>
+      </c>
+      <c r="B63" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>9c94b2cf-c951-4b58-bb1d-b76b5a2dfd04</v>
+      </c>
+      <c r="B64" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>88b7c743-1751-48c3-805b-49778285266f</v>
+      </c>
+      <c r="B65" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>230d4f49-82e2-4769-b14f-8a7ebf854b66</v>
+      </c>
+      <c r="B66" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>dd033e98-a353-4cdd-ae86-e7be5f70ac2e</v>
+      </c>
+      <c r="B67" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" t="str">
+        <f t="shared" ref="A68:A74" ca="1" si="1">LOWER(_xlfn.CONCAT(
+DEC2HEX(RANDBETWEEN(0,POWER(16,8)-1),8),"-",
+DEC2HEX(RANDBETWEEN(0,POWER(16,4)-1),4),"-",
+"4",DEC2HEX(RANDBETWEEN(0,POWER(16,3)-1),3),"-",
+DEC2HEX(RANDBETWEEN(8,11)),DEC2HEX(RANDBETWEEN(0,POWER(16,3)-1),3),"-",
+DEC2HEX(RANDBETWEEN(0,POWER(16,8)-1),8),
+DEC2HEX(RANDBETWEEN(0,POWER(16,4)-1),4)
+))</f>
+        <v>c633b3db-edbe-463e-83b7-71edef58aabc</v>
+      </c>
+      <c r="B68" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>45988edc-b99f-4b67-a7fa-bbdadb1cb87e</v>
+      </c>
+      <c r="B69" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>83740cf9-0093-4b47-9c34-85c2a58ec441</v>
+      </c>
+      <c r="B70" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>048de202-df6a-4577-b3a3-be956f5a755a</v>
+      </c>
+      <c r="B71" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>8cc7f0f9-0349-45a0-976b-cef4ab09cd09</v>
+      </c>
+      <c r="B72" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>4cfa83a2-4e84-49ac-9806-9814297c2ccc</v>
+      </c>
+      <c r="B73" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>62fe48cd-e543-4cb1-b92c-a7f9763830b0</v>
+      </c>
+      <c r="B74" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/docs/assets/3rdparty/source/icecream-flavours-IDs.xlsx
+++ b/docs/assets/3rdparty/source/icecream-flavours-IDs.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="142">
   <si>
     <t>Banana</t>
   </si>
@@ -249,6 +249,219 @@
   </si>
   <si>
     <t>Spundekas : based on the German cream cheese of the same name</t>
+  </si>
+  <si>
+    <t>Identifier</t>
+  </si>
+  <si>
+    <t>icf:1</t>
+  </si>
+  <si>
+    <t>icf:2</t>
+  </si>
+  <si>
+    <t>icf:3</t>
+  </si>
+  <si>
+    <t>icf:4</t>
+  </si>
+  <si>
+    <t>icf:5</t>
+  </si>
+  <si>
+    <t>icf:6</t>
+  </si>
+  <si>
+    <t>icf:7</t>
+  </si>
+  <si>
+    <t>icf:8</t>
+  </si>
+  <si>
+    <t>icf:9</t>
+  </si>
+  <si>
+    <t>icf:10</t>
+  </si>
+  <si>
+    <t>icf:11</t>
+  </si>
+  <si>
+    <t>icf:12</t>
+  </si>
+  <si>
+    <t>icf:13</t>
+  </si>
+  <si>
+    <t>icf:14</t>
+  </si>
+  <si>
+    <t>icf:15</t>
+  </si>
+  <si>
+    <t>icf:16</t>
+  </si>
+  <si>
+    <t>icf:17</t>
+  </si>
+  <si>
+    <t>icf:18</t>
+  </si>
+  <si>
+    <t>icf:19</t>
+  </si>
+  <si>
+    <t>icf:20</t>
+  </si>
+  <si>
+    <t>icf:21</t>
+  </si>
+  <si>
+    <t>icf:22</t>
+  </si>
+  <si>
+    <t>icf:23</t>
+  </si>
+  <si>
+    <t>icf:24</t>
+  </si>
+  <si>
+    <t>icf:25</t>
+  </si>
+  <si>
+    <t>icf:26</t>
+  </si>
+  <si>
+    <t>icf:27</t>
+  </si>
+  <si>
+    <t>icf:28</t>
+  </si>
+  <si>
+    <t>icf:29</t>
+  </si>
+  <si>
+    <t>icf:30</t>
+  </si>
+  <si>
+    <t>icf:31</t>
+  </si>
+  <si>
+    <t>icf:32</t>
+  </si>
+  <si>
+    <t>icf:33</t>
+  </si>
+  <si>
+    <t>icf:34</t>
+  </si>
+  <si>
+    <t>icf:35</t>
+  </si>
+  <si>
+    <t>icf:36</t>
+  </si>
+  <si>
+    <t>icf:37</t>
+  </si>
+  <si>
+    <t>icf:38</t>
+  </si>
+  <si>
+    <t>icf:39</t>
+  </si>
+  <si>
+    <t>icf:40</t>
+  </si>
+  <si>
+    <t>icf:41</t>
+  </si>
+  <si>
+    <t>icf:42</t>
+  </si>
+  <si>
+    <t>icf:43</t>
+  </si>
+  <si>
+    <t>icf:44</t>
+  </si>
+  <si>
+    <t>icf:45</t>
+  </si>
+  <si>
+    <t>icf:46</t>
+  </si>
+  <si>
+    <t>icf:47</t>
+  </si>
+  <si>
+    <t>icf:48</t>
+  </si>
+  <si>
+    <t>icf:49</t>
+  </si>
+  <si>
+    <t>icf:50</t>
+  </si>
+  <si>
+    <t>icf:51</t>
+  </si>
+  <si>
+    <t>icf:52</t>
+  </si>
+  <si>
+    <t>icf:53</t>
+  </si>
+  <si>
+    <t>icf:54</t>
+  </si>
+  <si>
+    <t>icf:55</t>
+  </si>
+  <si>
+    <t>icf:56</t>
+  </si>
+  <si>
+    <t>icf:57</t>
+  </si>
+  <si>
+    <t>icf:58</t>
+  </si>
+  <si>
+    <t>icf:59</t>
+  </si>
+  <si>
+    <t>icf:60</t>
+  </si>
+  <si>
+    <t>icf:61</t>
+  </si>
+  <si>
+    <t>icf:62</t>
+  </si>
+  <si>
+    <t>icf:63</t>
+  </si>
+  <si>
+    <t>icf:64</t>
+  </si>
+  <si>
+    <t>icf:65</t>
+  </si>
+  <si>
+    <t>icf:66</t>
+  </si>
+  <si>
+    <t>icf:67</t>
+  </si>
+  <si>
+    <t>icf:68</t>
+  </si>
+  <si>
+    <t>icf:69</t>
+  </si>
+  <si>
+    <t>icf:70</t>
   </si>
 </sst>
 </file>
@@ -627,677 +840,586 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FF9460-F418-CA44-84AF-DE772B3A7DA8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{83FF9460-F418-CA44-84AF-DE772B3A7DA8}">
   <dimension ref="A1:B74"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="48.1640625" customWidth="1"/>
     <col min="2" max="2" width="35.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>71</v>
+      </c>
       <c r="B1" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="str">
-        <f ca="1">LOWER(_xlfn.CONCAT(
-DEC2HEX(RANDBETWEEN(0,POWER(16,8)-1),8),"-",
-DEC2HEX(RANDBETWEEN(0,POWER(16,4)-1),4),"-",
-"4",DEC2HEX(RANDBETWEEN(0,POWER(16,3)-1),3),"-",
-DEC2HEX(RANDBETWEEN(8,11)),DEC2HEX(RANDBETWEEN(0,POWER(16,3)-1),3),"-",
-DEC2HEX(RANDBETWEEN(0,POWER(16,8)-1),8),
-DEC2HEX(RANDBETWEEN(0,POWER(16,4)-1),4)
-))</f>
-        <v>7b160f84-361e-417f-aef3-57aaae778e36</v>
+    <row r="2">
+      <c r="A2"/>
+    </row>
+    <row r="3" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>72</v>
       </c>
       <c r="B3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="str">
-        <f t="shared" ref="A4:A67" ca="1" si="0">LOWER(_xlfn.CONCAT(
-DEC2HEX(RANDBETWEEN(0,POWER(16,8)-1),8),"-",
-DEC2HEX(RANDBETWEEN(0,POWER(16,4)-1),4),"-",
-"4",DEC2HEX(RANDBETWEEN(0,POWER(16,3)-1),3),"-",
-DEC2HEX(RANDBETWEEN(8,11)),DEC2HEX(RANDBETWEEN(0,POWER(16,3)-1),3),"-",
-DEC2HEX(RANDBETWEEN(0,POWER(16,8)-1),8),
-DEC2HEX(RANDBETWEEN(0,POWER(16,4)-1),4)
-))</f>
-        <v>1b7d67e9-7f1a-4a51-b91e-b44e17e31c2c</v>
+    <row r="4" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>73</v>
       </c>
       <c r="B4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>f6e273e7-23c8-4cad-92dd-cb9663349b47</v>
+    <row r="5" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>74</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>04e3aad9-422b-48d0-b43d-80d1e28a7f46</v>
+    <row r="6" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>75</v>
       </c>
       <c r="B6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>170146c4-0f42-4414-91ba-61a9198efc79</v>
+    <row r="7" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>76</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>cf80d51f-821e-446c-aeab-58b80859ed49</v>
+    <row r="8" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>77</v>
       </c>
       <c r="B8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>5b03de59-40ab-4862-b9ea-927eaa017e60</v>
+    <row r="9" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>78</v>
       </c>
       <c r="B9" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>4e8018c9-6ac8-4649-8e6d-dd07f4c8bbb1</v>
+    <row r="10" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>79</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>00041781-f8a3-4959-8389-e5ddd1713226</v>
+    <row r="11" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>80</v>
       </c>
       <c r="B11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>19de5e74-293a-4e85-9b55-67d0b8e933e5</v>
+    <row r="12" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>81</v>
       </c>
       <c r="B12" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>44de53ec-9ce7-4c80-bc3d-7020c37b6133</v>
+    <row r="13" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>82</v>
       </c>
       <c r="B13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>bbea3fe3-1c39-4066-a0ab-99f2ccb53628</v>
+    <row r="14" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>83</v>
       </c>
       <c r="B14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>7bff714f-d9d9-473b-9ff9-19d4941eb65a</v>
+    <row r="15" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>84</v>
       </c>
       <c r="B15" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>78d3eb98-963b-4af5-8787-6a1619685c48</v>
+    <row r="16" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>85</v>
       </c>
       <c r="B16" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>8bd965d2-3c49-46f4-92f0-e65eb65b6d7a</v>
+    <row r="17" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>86</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>062de6fa-38dc-4ebb-b239-1e51d3b89303</v>
+    <row r="18" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>87</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>1b0cc14e-ab5f-4d1a-a3ed-b3fa1df250eb</v>
+    <row r="19" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>88</v>
       </c>
       <c r="B19" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>9804cdc4-7623-4714-8002-b95bfa42f4f6</v>
+    <row r="20" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>89</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>d22483e3-e9a4-4e9a-8739-736b57049f01</v>
+    <row r="21" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>90</v>
       </c>
       <c r="B21" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>ca11c2ce-1468-4107-8d63-95e3a3ec889f</v>
+    <row r="22" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>91</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>e7c665fc-e38e-4fb0-9e5b-4c422ba97512</v>
+    <row r="23" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>92</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>5b98668e-5454-430c-aa5b-0b266f840269</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>f9ec744d-4313-46cf-b847-70cb510d31d7</v>
+    <row r="24" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A24"/>
+    </row>
+    <row r="25" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>93</v>
       </c>
       <c r="B25" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>0cb6ff0e-dd72-4899-8364-60bb57935985</v>
+    <row r="26" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>94</v>
       </c>
       <c r="B26" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>0c5d8692-2484-437b-b0eb-d2ea4666dfe9</v>
+    <row r="27" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>95</v>
       </c>
       <c r="B27" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>ec8bdca2-5804-4814-a051-9a3dea143f2d</v>
+    <row r="28" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>96</v>
       </c>
       <c r="B28" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>057108ce-4561-4708-bb16-c97b070c9174</v>
+    <row r="29" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>97</v>
       </c>
       <c r="B29" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>7dfbb71b-4ce1-42a9-bf92-d783499cf216</v>
+    <row r="30" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>98</v>
       </c>
       <c r="B30" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>23f62340-3f68-4d5e-b6a6-9807cadc3ca6</v>
+    <row r="31" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>99</v>
       </c>
       <c r="B31" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>fa098773-8ea0-4b7f-9eef-c905a6079a57</v>
+    <row r="32" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>100</v>
       </c>
       <c r="B32" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>1807ea36-1fea-440a-b44e-ad73aa35d804</v>
+    <row r="33" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>101</v>
       </c>
       <c r="B33" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>e450e82a-80de-4892-81ef-47f347c90810</v>
+    <row r="34" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>102</v>
       </c>
       <c r="B34" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2d341970-764b-412e-8d1f-74e8a0e4258d</v>
+    <row r="35" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>103</v>
       </c>
       <c r="B35" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>a67b7766-0678-4d7f-9f51-c5c7bfb69bdf</v>
+    <row r="36" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>104</v>
       </c>
       <c r="B36" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>25444a85-caa1-4f0a-a1a2-c1bdfacd68ea</v>
+    <row r="37" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>105</v>
       </c>
       <c r="B37" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>86f37cd2-ade6-4cec-b74e-51a49099be97</v>
+    <row r="38" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>106</v>
       </c>
       <c r="B38" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>4e98b000-1c77-42a8-be9d-41f26e98a83b</v>
+    <row r="39" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>107</v>
       </c>
       <c r="B39" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>1bb203c3-6c4e-4f09-bbdc-459d96a4a202</v>
+    <row r="40" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>108</v>
       </c>
       <c r="B40" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>12bfaf5a-5e2f-40b2-a74f-b92fe565c1e6</v>
+    <row r="41" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>109</v>
       </c>
       <c r="B41" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>64ea1a0f-f5b8-45c2-a516-57a5c7c67c31</v>
+    <row r="42" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>110</v>
       </c>
       <c r="B42" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>8a47be0e-71c8-4793-9ffb-d0eae6d4918f</v>
+    <row r="43" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>111</v>
       </c>
       <c r="B43" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>9ba2647c-2eb0-43d9-a63e-f80c01d5a170</v>
+    <row r="44" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>112</v>
       </c>
       <c r="B44" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>888a8366-9523-4cb7-b268-d85ccfc9c390</v>
+    <row r="45" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>113</v>
       </c>
       <c r="B45" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>e343fee9-c50e-488c-9040-3c1ad0208292</v>
+    <row r="46" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>114</v>
       </c>
       <c r="B46" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>59c5f961-5b89-4a6b-93e4-f884377255b1</v>
+    <row r="47" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>115</v>
       </c>
       <c r="B47" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>d890d2f8-83b0-45f8-88a2-c96df44dfc52</v>
+    <row r="48" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>116</v>
       </c>
       <c r="B48" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>08212cd3-3985-4c45-adc6-6d8955f210c3</v>
+    <row r="49" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>117</v>
       </c>
       <c r="B49" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>a948bd7f-a30e-4bad-b595-3a45b10b0db0</v>
+    <row r="50" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>118</v>
       </c>
       <c r="B50" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A51" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>ca4bb557-abf8-44d8-a24d-6ac5277c6ff5</v>
+    <row r="51" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>119</v>
       </c>
       <c r="B51" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A52" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>f58cc31e-5820-4405-8f7e-aefda29dd5ac</v>
+    <row r="52" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>120</v>
       </c>
       <c r="B52" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A53" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>98960d08-12e5-40b0-90c5-0c37a2a17a9c</v>
+    <row r="53" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>121</v>
       </c>
       <c r="B53" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A54" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>47ab46a8-1e05-4676-b2ba-447ca72d7ef2</v>
+    <row r="54" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>122</v>
       </c>
       <c r="B54" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A55" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>a72efc96-e261-446a-ac49-784712bd4011</v>
+    <row r="55" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>123</v>
       </c>
       <c r="B55" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A56" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>5db09078-d358-4962-96d8-04a176e3e891</v>
+    <row r="56" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>124</v>
       </c>
       <c r="B56" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A57" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>d130fffe-5b33-48da-bb69-7bcbe3b25aa2</v>
+    <row r="57" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>125</v>
       </c>
       <c r="B57" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A58" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>c44927ad-c1d8-46ab-97ce-b661fc446158</v>
+    <row r="58" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>126</v>
       </c>
       <c r="B58" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A59" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>b6efc05c-2ee7-4633-aadb-2b2939e43614</v>
+    <row r="59" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>127</v>
       </c>
       <c r="B59" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A60" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>f58d780a-ca40-4782-a752-cbc64cc41350</v>
+    <row r="60" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>128</v>
       </c>
       <c r="B60" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A61" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>b001266b-ef05-4572-827e-c979de02018a</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A62" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>beebca3e-8f17-48ed-9f2f-8c981e849127</v>
+    <row r="61" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A61"/>
+    </row>
+    <row r="62" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>129</v>
       </c>
       <c r="B62" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A63" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>ee4ffef7-7b92-4313-ba03-b75685cfa35f</v>
+    <row r="63" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>130</v>
       </c>
       <c r="B63" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A64" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>9c94b2cf-c951-4b58-bb1d-b76b5a2dfd04</v>
+    <row r="64" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>131</v>
       </c>
       <c r="B64" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A65" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>88b7c743-1751-48c3-805b-49778285266f</v>
+    <row r="65" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>132</v>
       </c>
       <c r="B65" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A66" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>230d4f49-82e2-4769-b14f-8a7ebf854b66</v>
+    <row r="66" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>133</v>
       </c>
       <c r="B66" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A67" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>dd033e98-a353-4cdd-ae86-e7be5f70ac2e</v>
+    <row r="67" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>134</v>
       </c>
       <c r="B67" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A68" t="str">
-        <f t="shared" ref="A68:A74" ca="1" si="1">LOWER(_xlfn.CONCAT(
-DEC2HEX(RANDBETWEEN(0,POWER(16,8)-1),8),"-",
-DEC2HEX(RANDBETWEEN(0,POWER(16,4)-1),4),"-",
-"4",DEC2HEX(RANDBETWEEN(0,POWER(16,3)-1),3),"-",
-DEC2HEX(RANDBETWEEN(8,11)),DEC2HEX(RANDBETWEEN(0,POWER(16,3)-1),3),"-",
-DEC2HEX(RANDBETWEEN(0,POWER(16,8)-1),8),
-DEC2HEX(RANDBETWEEN(0,POWER(16,4)-1),4)
-))</f>
-        <v>c633b3db-edbe-463e-83b7-71edef58aabc</v>
+    <row r="68" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>135</v>
       </c>
       <c r="B68" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A69" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>45988edc-b99f-4b67-a7fa-bbdadb1cb87e</v>
+    <row r="69" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>136</v>
       </c>
       <c r="B69" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A70" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>83740cf9-0093-4b47-9c34-85c2a58ec441</v>
+    <row r="70" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>137</v>
       </c>
       <c r="B70" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A71" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>048de202-df6a-4577-b3a3-be956f5a755a</v>
+    <row r="71" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>138</v>
       </c>
       <c r="B71" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A72" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>8cc7f0f9-0349-45a0-976b-cef4ab09cd09</v>
+    <row r="72" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>139</v>
       </c>
       <c r="B72" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A73" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>4cfa83a2-4e84-49ac-9806-9814297c2ccc</v>
+    <row r="73" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>140</v>
       </c>
       <c r="B73" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A74" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>62fe48cd-e543-4cb1-b92c-a7f9763830b0</v>
+    <row r="74" spans="1:2" ns3:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>141</v>
       </c>
       <c r="B74" t="s">
         <v>67</v>
